--- a/work_request_forms/032_elevator_music_system_repair_request_form--work_request_forms.xlsx
+++ b/work_request_forms/032_elevator_music_system_repair_request_form--work_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>facility_name</t>
+          <t>facility_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Facility Name</t>
+          <t>Facility Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>facility_address</t>
+          <t>facility_address_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Facility Address</t>
+          <t>Facility Address 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>facility_manager</t>
+          <t>facility_manager_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Facility Manager</t>
+          <t>Facility Manager 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Assigned To 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>facility_name</t>
+          <t>facility_name_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Facility Name</t>
+          <t>Facility Name 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1129,8 +1129,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'working'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Working'}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'not_working'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Not Working'}</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'maintenance_required'}</t>
+          <t>maintenance_required</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Maintenance Required'}</t>
+          <t>Maintenance Required</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'satellite'}</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Satellite'}</t>
+          <t>Satellite</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'streaming'}</t>
+          <t>streaming</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Streaming'}</t>
+          <t>Streaming</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'mp3'}</t>
+          <t>mp3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'MP3'}</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'wav'}</t>
+          <t>wav</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'WAV'}</t>
+          <t>WAV</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'flac'}</t>
+          <t>flac</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'FLAC'}</t>
+          <t>FLAC</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'24/7'}</t>
+          <t>24/7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '24/7'}</t>
+          <t>24/7</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'on_demand'}</t>
+          <t>on_demand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'On Demand'}</t>
+          <t>On Demand</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -1442,51 +1442,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
